--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T11:11:22-05:00</t>
+    <t>2023-05-04T21:49:21-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3845,17 +3845,17 @@
   <dimension ref="A1:AP346"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="74.34765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.0546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.8828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.8984375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="73.5" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="28.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3864,28 +3864,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.7109375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.0859375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.30859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.77734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.75390625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.09765625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.984375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.30078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.19140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="75.3359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="242.69140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="103.8828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="37.7109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T21:49:21-05:00</t>
+    <t>2023-05-05T10:50:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T16:25:42-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3863,17 +3863,17 @@
   <dimension ref="A1:AP346"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="74.34375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.0546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.87890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="66.67578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.9921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="25.00390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="100.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3882,28 +3882,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.77734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.75" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.09765625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.19140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.140625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.9609375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="239.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="103.87890625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="37.7109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.10</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-04-23T10:10:52-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -493,7 +493,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -683,7 +683,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -5230,7 +5230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>358</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>398</v>
       </c>
@@ -19628,7 +19628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
         <v>686</v>
       </c>
@@ -31890,7 +31890,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" hidden="true">
+    <row r="232">
       <c r="A232" t="s" s="2">
         <v>862</v>
       </c>
@@ -45850,12 +45850,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP346">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-06-10T07:35:08-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -493,7 +493,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -683,7 +683,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -5230,7 +5230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>358</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>398</v>
       </c>
@@ -19628,7 +19628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
         <v>686</v>
       </c>
@@ -31890,7 +31890,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" hidden="true">
+    <row r="232">
       <c r="A232" t="s" s="2">
         <v>862</v>
       </c>
@@ -45850,12 +45850,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP346">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
+++ b/publication/web-root/cibmtr-reporting/StructureDefinition-cibmtr-cytogenetics.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:49:22-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
